--- a/nba_rosters_plantilla.xlsx
+++ b/nba_rosters_plantilla.xlsx
@@ -554,26 +554,26 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Jrue Holiday</t>
+          <t>Payton Pritchard</t>
         </is>
       </c>
       <c r="D2" s="5" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>2.3</v>
+        <v>-0.6</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H2" s="3" t="b">
         <v>0</v>
       </c>
       <c r="I2" s="5" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="3">
@@ -596,19 +596,19 @@
         <v>34</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H3" s="3" t="b">
         <v>0</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>20.5</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="4">
@@ -624,26 +624,26 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Jaylen Brown</t>
+          <t>Paul George</t>
         </is>
       </c>
       <c r="D4" s="5" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H4" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>22.5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5">
@@ -666,13 +666,13 @@
         <v>36</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="H5" s="3" t="b">
         <v>1</v>
@@ -694,26 +694,26 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Kristaps Porzingis</t>
+          <t>Neemias Queta</t>
         </is>
       </c>
       <c r="D6" s="5" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>2.9</v>
+        <v>0.2</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="H6" s="3" t="b">
         <v>0</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>19.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="7">
@@ -729,17 +729,17 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Pritchard / Horford / Hauser</t>
+          <t>Robinson / Hauser / Scheierman</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0.9</v>
+        <v>-0.7</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.6</v>
+        <v>-0.5</v>
       </c>
       <c r="G7" s="5" t="n">
         <v>0</v>
@@ -764,26 +764,26 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>Dennis Schroder</t>
+          <t>Egor Demin</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>-0.6</v>
+        <v>-0.3</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="H8" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="9">
@@ -799,26 +799,26 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>Cam Thomas</t>
+          <t>Keon Ellis</t>
         </is>
       </c>
       <c r="D9" s="8" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>1.6</v>
+        <v>0.3</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>-1.8</v>
+        <v>0.8</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="H9" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" s="8" t="n">
-        <v>23.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="10">
@@ -834,26 +834,26 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Cameron Johnson</t>
+          <t>Michael Porter Jr.</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>-0.2</v>
+        <v>-0.8</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H10" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>17.5</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="11">
@@ -869,26 +869,26 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>Dorian Finney-Smith</t>
+          <t>Julius Randle</t>
         </is>
       </c>
       <c r="D11" s="8" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>-1.2</v>
+        <v>1.8</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>0.8</v>
+        <v>-0.9</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="H11" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>12.5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
@@ -904,26 +904,26 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Nic Claxton</t>
+          <t>Day'Ron Sharpe</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>-0.5</v>
+        <v>-0.2</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H12" s="6" t="b">
         <v>0</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>14.5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
@@ -939,14 +939,14 @@
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>Simmons / Clowney / Wilson</t>
+          <t>Brown Jr. / Traore / Wagner</t>
         </is>
       </c>
       <c r="D13" s="8" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E13" s="8" t="n">
-        <v>-1.6</v>
+        <v>-0.8</v>
       </c>
       <c r="F13" s="8" t="n">
         <v>-0.6</v>
@@ -981,13 +981,13 @@
         <v>36</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="F14" s="5" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="G14" s="5" t="n">
         <v>-0.4</v>
-      </c>
-      <c r="G14" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="H14" s="3" t="b">
         <v>1</v>
@@ -1013,13 +1013,13 @@
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="G15" s="5" t="n">
         <v>0</v>
@@ -1028,7 +1028,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>19.5</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="16">
@@ -1044,26 +1044,26 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>OG Anunoby</t>
+          <t>Josh Hart</t>
         </is>
       </c>
       <c r="D16" s="5" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>3.1</v>
+        <v>1</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="H16" s="3" t="b">
         <v>0</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>18.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="17">
@@ -1079,17 +1079,17 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Josh Hart</t>
+          <t>OG Anunoby</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="G17" s="5" t="n">
         <v>0</v>
@@ -1098,7 +1098,7 @@
         <v>0</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -1118,16 +1118,16 @@
         </is>
       </c>
       <c r="D18" s="5" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0.5</v>
+        <v>-0.1</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="H18" s="3" t="b">
         <v>1</v>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>McBride / Achiuwa / Payne</t>
+          <t>Shamet / McBride / Drummond</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>-0.4</v>
+        <v>-0.9</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>0.6</v>
+        <v>-0.8</v>
       </c>
       <c r="G19" s="5" t="n">
         <v>0</v>
@@ -1191,19 +1191,19 @@
         <v>36</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>-0.3</v>
+        <v>0.2</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="H20" s="6" t="b">
         <v>1</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>25.5</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="21">
@@ -1219,26 +1219,26 @@
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>Kelly Oubre Jr.</t>
+          <t>VJ Edgecombe</t>
         </is>
       </c>
       <c r="D21" s="8" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>-0.3</v>
+        <v>0.8</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="H21" s="6" t="b">
         <v>0</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="22">
@@ -1254,20 +1254,20 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>Paul George</t>
+          <t>Jaylen Brown</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H22" s="6" t="b">
         <v>0</v>
@@ -1289,26 +1289,26 @@
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>Caleb Martin</t>
+          <t>LeBron James</t>
         </is>
       </c>
       <c r="D23" s="8" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>-0.6</v>
+        <v>3.9</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="H23" s="6" t="b">
         <v>0</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>13.5</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="24">
@@ -1328,22 +1328,22 @@
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>3.2</v>
+        <v>0.7</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="H24" s="6" t="b">
         <v>1</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>28.5</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="25">
@@ -1359,17 +1359,17 @@
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>Lowry / Drummond / McCain</t>
+          <t>Wade / Caldwell-Pope / Barlow</t>
         </is>
       </c>
       <c r="D25" s="8" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E25" s="8" t="n">
-        <v>-1.4</v>
+        <v>-1.1</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>-0.2</v>
+        <v>-0.8</v>
       </c>
       <c r="G25" s="8" t="n">
         <v>0</v>
@@ -1401,19 +1401,19 @@
         <v>33</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>-0.3</v>
+        <v>-0.9</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="H26" s="3" t="b">
         <v>0</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="27">
@@ -1429,26 +1429,26 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Gradey Dick</t>
+          <t>RJ Barrett</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>-1.4</v>
+        <v>-0.6</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H27" s="3" t="b">
         <v>0</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>14.5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28">
@@ -1464,26 +1464,26 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>RJ Barrett</t>
+          <t>Kawhi Leonard</t>
         </is>
       </c>
       <c r="D28" s="5" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>1.1</v>
+        <v>3.5</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>-0.9</v>
+        <v>1.2</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0</v>
+        <v>-0.7</v>
       </c>
       <c r="H28" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>20.5</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="29">
@@ -1506,19 +1506,19 @@
         <v>35</v>
       </c>
       <c r="E29" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F29" s="5" t="n">
         <v>1.8</v>
       </c>
-      <c r="F29" s="5" t="n">
-        <v>1.2</v>
-      </c>
       <c r="G29" s="5" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="H29" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>19.5</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="30">
@@ -1538,7 +1538,7 @@
         </is>
       </c>
       <c r="D30" s="5" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E30" s="5" t="n">
         <v>0.3</v>
@@ -1547,13 +1547,13 @@
         <v>1.4</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="H30" s="3" t="b">
         <v>0</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>15.5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31">
@@ -1569,17 +1569,17 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Boucher / Agbaji / Mitchell</t>
+          <t>Murray-Boyles / Walter / Anderson</t>
         </is>
       </c>
       <c r="D31" s="5" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>-1.8</v>
+        <v>-1.2</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>-1.1</v>
+        <v>-1</v>
       </c>
       <c r="G31" s="5" t="n">
         <v>0</v>
@@ -1608,22 +1608,22 @@
         </is>
       </c>
       <c r="D32" s="8" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>-0.8</v>
+        <v>0</v>
       </c>
       <c r="G32" s="8" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="H32" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32" s="8" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="33">
@@ -1639,26 +1639,26 @@
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>Coby White</t>
+          <t>Norman Powell</t>
         </is>
       </c>
       <c r="D33" s="8" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E33" s="8" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>-0.7</v>
+        <v>-0.8</v>
       </c>
       <c r="G33" s="8" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="H33" s="6" t="b">
         <v>1</v>
       </c>
       <c r="I33" s="8" t="n">
-        <v>19.5</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="34">
@@ -1674,26 +1674,26 @@
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Zach LaVine</t>
+          <t>Matas Buzelis</t>
         </is>
       </c>
       <c r="D34" s="8" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E34" s="8" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>-1.1</v>
+        <v>0.3</v>
       </c>
       <c r="G34" s="8" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="H34" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I34" s="8" t="n">
-        <v>22.5</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="35">
@@ -1709,26 +1709,26 @@
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>Patrick Williams</t>
+          <t>Caleb Wilson</t>
         </is>
       </c>
       <c r="D35" s="8" t="n">
         <v>28</v>
       </c>
       <c r="E35" s="8" t="n">
-        <v>-1.3</v>
+        <v>0.5</v>
       </c>
       <c r="F35" s="8" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="G35" s="8" t="n">
         <v>0.5</v>
       </c>
-      <c r="G35" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="H35" s="6" t="b">
         <v>0</v>
       </c>
       <c r="I35" s="8" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="36">
@@ -1744,17 +1744,17 @@
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>Nikola Vucevic</t>
+          <t>Nic Claxton</t>
         </is>
       </c>
       <c r="D36" s="8" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E36" s="8" t="n">
-        <v>0.8</v>
+        <v>-0.2</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>-0.6</v>
+        <v>1.9</v>
       </c>
       <c r="G36" s="8" t="n">
         <v>0</v>
@@ -1763,7 +1763,7 @@
         <v>0</v>
       </c>
       <c r="I36" s="8" t="n">
-        <v>17.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="37">
@@ -1779,17 +1779,17 @@
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>Dosunmu / Ball / Smith</t>
+          <t>Miller / Smith / Essengue</t>
         </is>
       </c>
       <c r="D37" s="8" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="E37" s="8" t="n">
-        <v>-1.1</v>
+        <v>-0.7</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>-0.2</v>
+        <v>-0.5</v>
       </c>
       <c r="G37" s="8" t="n">
         <v>0</v>
@@ -1814,26 +1814,26 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Darius Garland</t>
+          <t>James Harden</t>
         </is>
       </c>
       <c r="D38" s="5" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="H38" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>19.5</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="39">
@@ -1856,13 +1856,13 @@
         <v>35</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="H39" s="3" t="b">
         <v>1</v>
@@ -1884,26 +1884,26 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Max Strus</t>
+          <t>Peyton Watson</t>
         </is>
       </c>
       <c r="D40" s="5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="F40" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G40" s="5" t="n">
         <v>0.4</v>
       </c>
-      <c r="G40" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="H40" s="3" t="b">
         <v>0</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="41">
@@ -1926,13 +1926,13 @@
         <v>33</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H41" s="3" t="b">
         <v>0</v>
@@ -1958,22 +1958,22 @@
         </is>
       </c>
       <c r="D42" s="5" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="H42" s="3" t="b">
         <v>0</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>18.5</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="43">
@@ -1989,17 +1989,17 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>LeVert / Jerome / Wade</t>
+          <t>Merrill / Tyson / Hezonja</t>
         </is>
       </c>
       <c r="D43" s="5" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>0.7</v>
+        <v>-0.8</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>0.6</v>
+        <v>-0.6</v>
       </c>
       <c r="G43" s="5" t="n">
         <v>0</v>
@@ -2028,22 +2028,22 @@
         </is>
       </c>
       <c r="D44" s="8" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E44" s="8" t="n">
-        <v>2.2</v>
+        <v>4.4</v>
       </c>
       <c r="F44" s="8" t="n">
-        <v>-0.9</v>
+        <v>0.2</v>
       </c>
       <c r="G44" s="8" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="H44" s="6" t="b">
         <v>1</v>
       </c>
       <c r="I44" s="8" t="n">
-        <v>24.5</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="45">
@@ -2059,26 +2059,26 @@
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>Jaden Ivey</t>
+          <t>Duncan Robinson</t>
         </is>
       </c>
       <c r="D45" s="8" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E45" s="8" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="F45" s="8" t="n">
         <v>-1.4</v>
       </c>
       <c r="G45" s="8" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H45" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I45" s="8" t="n">
-        <v>16.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="46">
@@ -2094,20 +2094,20 @@
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>Tim Hardaway Jr.</t>
+          <t>Ausar Thompson</t>
         </is>
       </c>
       <c r="D46" s="8" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E46" s="8" t="n">
-        <v>-0.4</v>
+        <v>0.4</v>
       </c>
       <c r="F46" s="8" t="n">
-        <v>-1.5</v>
+        <v>2</v>
       </c>
       <c r="G46" s="8" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="H46" s="6" t="b">
         <v>0</v>
@@ -2129,17 +2129,17 @@
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>Tobias Harris</t>
+          <t>John Collins</t>
         </is>
       </c>
       <c r="D47" s="8" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E47" s="8" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>-0.3</v>
+        <v>-0.2</v>
       </c>
       <c r="G47" s="8" t="n">
         <v>0</v>
@@ -2148,7 +2148,7 @@
         <v>0</v>
       </c>
       <c r="I47" s="8" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="48">
@@ -2168,22 +2168,22 @@
         </is>
       </c>
       <c r="D48" s="8" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E48" s="8" t="n">
-        <v>0.2</v>
+        <v>1.9</v>
       </c>
       <c r="F48" s="8" t="n">
-        <v>-0.6</v>
+        <v>0.8</v>
       </c>
       <c r="G48" s="8" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="H48" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I48" s="8" t="n">
-        <v>15.5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="49">
@@ -2199,17 +2199,17 @@
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>Beasley / Thompson / Stewart</t>
+          <t>Joe / Jenkins / Holland</t>
         </is>
       </c>
       <c r="D49" s="8" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E49" s="8" t="n">
-        <v>-2.2</v>
+        <v>-0.9</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>-0.7</v>
+        <v>-0.8</v>
       </c>
       <c r="G49" s="8" t="n">
         <v>0</v>
@@ -2238,16 +2238,16 @@
         </is>
       </c>
       <c r="D50" s="5" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>-1.3</v>
+        <v>0.3</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="H50" s="3" t="b">
         <v>1</v>
@@ -2276,19 +2276,19 @@
         <v>30</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F51" s="5" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="H51" s="3" t="b">
         <v>0</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="52">
@@ -2308,22 +2308,22 @@
         </is>
       </c>
       <c r="D52" s="5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="F52" s="5" t="n">
         <v>0.6</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H52" s="3" t="b">
         <v>0</v>
       </c>
       <c r="I52" s="5" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="53">
@@ -2346,7 +2346,7 @@
         <v>34</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="F53" s="5" t="n">
         <v>0.4</v>
@@ -2374,26 +2374,26 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Myles Turner</t>
+          <t>Ivica Zubac</t>
         </is>
       </c>
       <c r="D54" s="5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="F54" s="5" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="H54" s="3" t="b">
         <v>0</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="55">
@@ -2409,17 +2409,17 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Mathurin / McConnell / Toppin</t>
+          <t>Oubre / McConnell / Nance Jr.</t>
         </is>
       </c>
       <c r="D55" s="5" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>0.8</v>
+        <v>-1.1</v>
       </c>
       <c r="F55" s="5" t="n">
-        <v>-1.2</v>
+        <v>-0.8</v>
       </c>
       <c r="G55" s="5" t="n">
         <v>0</v>
@@ -2444,26 +2444,26 @@
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>Damian Lillard</t>
+          <t>Ryan Rollins</t>
         </is>
       </c>
       <c r="D56" s="8" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E56" s="8" t="n">
-        <v>3.9</v>
+        <v>0.6</v>
       </c>
       <c r="F56" s="8" t="n">
-        <v>-1.2</v>
+        <v>0.1</v>
       </c>
       <c r="G56" s="8" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H56" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I56" s="8" t="n">
-        <v>24.5</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="57">
@@ -2479,26 +2479,26 @@
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>Gary Trent Jr.</t>
+          <t>Tyler Herro</t>
         </is>
       </c>
       <c r="D57" s="8" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E57" s="8" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="F57" s="8" t="n">
-        <v>-0.3</v>
+        <v>-1.1</v>
       </c>
       <c r="G57" s="8" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H57" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I57" s="8" t="n">
-        <v>15.5</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="58">
@@ -2514,20 +2514,20 @@
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>Taurean Prince</t>
+          <t>Jaime Jaquez Jr.</t>
         </is>
       </c>
       <c r="D58" s="8" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E58" s="8" t="n">
-        <v>-0.4</v>
+        <v>0.2</v>
       </c>
       <c r="F58" s="8" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="G58" s="8" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="H58" s="6" t="b">
         <v>0</v>
@@ -2549,17 +2549,17 @@
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>Giannis Antetokounmpo</t>
+          <t>Kyle Kuzma</t>
         </is>
       </c>
       <c r="D59" s="8" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E59" s="8" t="n">
-        <v>5.5</v>
+        <v>0.7</v>
       </c>
       <c r="F59" s="8" t="n">
-        <v>2.3</v>
+        <v>-0.8</v>
       </c>
       <c r="G59" s="8" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
         <v>1</v>
       </c>
       <c r="I59" s="8" t="n">
-        <v>30.5</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="60">
@@ -2584,26 +2584,26 @@
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>Brook Lopez</t>
+          <t>Myles Turner</t>
         </is>
       </c>
       <c r="D60" s="8" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E60" s="8" t="n">
         <v>0.3</v>
       </c>
       <c r="F60" s="8" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="G60" s="8" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="H60" s="6" t="b">
         <v>0</v>
       </c>
       <c r="I60" s="8" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="61">
@@ -2619,17 +2619,17 @@
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>Portis / Wright / Connaughton</t>
+          <t>Burries / Ware / Jakucionis</t>
         </is>
       </c>
       <c r="D61" s="8" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E61" s="8" t="n">
-        <v>-0.9</v>
+        <v>-1.2</v>
       </c>
       <c r="F61" s="8" t="n">
-        <v>-0.4</v>
+        <v>-1</v>
       </c>
       <c r="G61" s="8" t="n">
         <v>0</v>
@@ -2658,13 +2658,13 @@
         </is>
       </c>
       <c r="D62" s="5" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="F62" s="5" t="n">
-        <v>-0.1</v>
+        <v>-0.3</v>
       </c>
       <c r="G62" s="5" t="n">
         <v>0</v>
@@ -2673,7 +2673,7 @@
         <v>1</v>
       </c>
       <c r="I62" s="5" t="n">
-        <v>20.5</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="63">
@@ -2693,22 +2693,22 @@
         </is>
       </c>
       <c r="D63" s="5" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E63" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F63" s="5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G63" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="F63" s="5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="H63" s="3" t="b">
         <v>0</v>
       </c>
       <c r="I63" s="5" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="64">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Michael Porter Jr.</t>
+          <t>Cameron Johnson</t>
         </is>
       </c>
       <c r="D64" s="5" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>0.3</v>
+        <v>-0.2</v>
       </c>
       <c r="G64" s="5" t="n">
         <v>0</v>
@@ -2743,7 +2743,7 @@
         <v>0</v>
       </c>
       <c r="I64" s="5" t="n">
-        <v>19.5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="65">
@@ -2766,19 +2766,19 @@
         <v>33</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="F65" s="5" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H65" s="3" t="b">
         <v>0</v>
       </c>
       <c r="I65" s="5" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="66">
@@ -2801,19 +2801,19 @@
         <v>36</v>
       </c>
       <c r="E66" s="5" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="F66" s="5" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="H66" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I66" s="5" t="n">
-        <v>26.5</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="67">
@@ -2829,17 +2829,17 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Westbrook / Watson / Strawther</t>
+          <t>DeRozan / Bagley / Diallo</t>
         </is>
       </c>
       <c r="D67" s="5" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>-1.4</v>
+        <v>-0.7</v>
       </c>
       <c r="F67" s="5" t="n">
-        <v>0.2</v>
+        <v>-0.5</v>
       </c>
       <c r="G67" s="5" t="n">
         <v>0</v>
@@ -2864,26 +2864,26 @@
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>Mike Conley</t>
+          <t>LaMelo Ball</t>
         </is>
       </c>
       <c r="D68" s="8" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E68" s="8" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="F68" s="8" t="n">
-        <v>0.7</v>
+        <v>-1</v>
       </c>
       <c r="G68" s="8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="H68" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I68" s="8" t="n">
-        <v>17.5</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="69">
@@ -2906,19 +2906,19 @@
         <v>36</v>
       </c>
       <c r="E69" s="8" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="F69" s="8" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="G69" s="8" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H69" s="6" t="b">
         <v>1</v>
       </c>
       <c r="I69" s="8" t="n">
-        <v>26.5</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="70">
@@ -2938,22 +2938,22 @@
         </is>
       </c>
       <c r="D70" s="8" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E70" s="8" t="n">
-        <v>-0.6</v>
+        <v>1.4</v>
       </c>
       <c r="F70" s="8" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="G70" s="8" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="H70" s="6" t="b">
         <v>0</v>
       </c>
       <c r="I70" s="8" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="71">
@@ -2969,26 +2969,26 @@
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>Julius Randle</t>
+          <t>Jonathan Kuminga</t>
         </is>
       </c>
       <c r="D71" s="8" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E71" s="8" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="F71" s="8" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G71" s="8" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="H71" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I71" s="8" t="n">
-        <v>20.5</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="72">
@@ -3008,22 +3008,22 @@
         </is>
       </c>
       <c r="D72" s="8" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E72" s="8" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="F72" s="8" t="n">
-        <v>3.8</v>
+        <v>2</v>
       </c>
       <c r="G72" s="8" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="H72" s="6" t="b">
         <v>0</v>
       </c>
       <c r="I72" s="8" t="n">
-        <v>17.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="73">
@@ -3039,17 +3039,17 @@
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>Reid / DiVincenzo / Alexander-Walker</t>
+          <t>Dosunmu / Hyland / Green</t>
         </is>
       </c>
       <c r="D73" s="8" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E73" s="8" t="n">
-        <v>0.4</v>
+        <v>-0.8</v>
       </c>
       <c r="F73" s="8" t="n">
-        <v>1.3</v>
+        <v>-0.6</v>
       </c>
       <c r="G73" s="8" t="n">
         <v>0</v>
@@ -3081,19 +3081,19 @@
         <v>35</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>6.1</v>
+        <v>7</v>
       </c>
       <c r="F74" s="5" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H74" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I74" s="5" t="n">
-        <v>29.5</v>
+        <v>31</v>
       </c>
     </row>
     <row r="75">
@@ -3109,26 +3109,26 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Luguentz Dort</t>
+          <t>Cason Wallace</t>
         </is>
       </c>
       <c r="D75" s="5" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E75" s="5" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="F75" s="5" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H75" s="3" t="b">
         <v>0</v>
       </c>
       <c r="I75" s="5" t="n">
-        <v>15.5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="76">
@@ -3144,26 +3144,26 @@
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>Alex Caruso</t>
+          <t>Jalen Williams</t>
         </is>
       </c>
       <c r="D76" s="5" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>0.3</v>
+        <v>2.8</v>
       </c>
       <c r="F76" s="5" t="n">
-        <v>3.4</v>
+        <v>0.6</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H76" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I76" s="5" t="n">
-        <v>14.5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="77">
@@ -3179,26 +3179,26 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>Jalen Williams</t>
+          <t>Chet Holmgren</t>
         </is>
       </c>
       <c r="D77" s="5" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E77" s="5" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="F77" s="5" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="G77" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H77" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I77" s="5" t="n">
-        <v>20.5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="78">
@@ -3214,26 +3214,26 @@
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>Chet Holmgren</t>
+          <t>Isaiah Hartenstein</t>
         </is>
       </c>
       <c r="D78" s="5" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="F78" s="5" t="n">
-        <v>3.5</v>
+        <v>1.9</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="H78" s="3" t="b">
         <v>0</v>
       </c>
       <c r="I78" s="5" t="n">
-        <v>19.5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="79">
@@ -3249,17 +3249,17 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>Wallace / Joe / Wiggins</t>
+          <t>Mitchell / Mara / Jaylin Williams</t>
         </is>
       </c>
       <c r="D79" s="5" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E79" s="5" t="n">
-        <v>0.6</v>
+        <v>-0.9</v>
       </c>
       <c r="F79" s="5" t="n">
-        <v>1</v>
+        <v>-0.8</v>
       </c>
       <c r="G79" s="5" t="n">
         <v>0</v>
@@ -3284,26 +3284,26 @@
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>Scoot Henderson</t>
+          <t>Ja Morant</t>
         </is>
       </c>
       <c r="D80" s="8" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E80" s="8" t="n">
-        <v>-1.4</v>
+        <v>4.2</v>
       </c>
       <c r="F80" s="8" t="n">
-        <v>-1.2</v>
+        <v>-1.1</v>
       </c>
       <c r="G80" s="8" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="H80" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I80" s="8" t="n">
-        <v>12.5</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="81">
@@ -3319,26 +3319,26 @@
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>Anfernee Simons</t>
+          <t>Damian Lillard</t>
         </is>
       </c>
       <c r="D81" s="8" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E81" s="8" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="F81" s="8" t="n">
-        <v>-2.1</v>
+        <v>-1.4</v>
       </c>
       <c r="G81" s="8" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H81" s="6" t="b">
         <v>1</v>
       </c>
       <c r="I81" s="8" t="n">
-        <v>21.5</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="82">
@@ -3354,26 +3354,26 @@
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>Deni Avdija</t>
+          <t>Toumani Camara</t>
         </is>
       </c>
       <c r="D82" s="8" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E82" s="8" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="F82" s="8" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="G82" s="8" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="H82" s="6" t="b">
         <v>0</v>
       </c>
       <c r="I82" s="8" t="n">
-        <v>16.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="83">
@@ -3389,26 +3389,26 @@
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>Jerami Grant</t>
+          <t>Deni Avdija</t>
         </is>
       </c>
       <c r="D83" s="8" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E83" s="8" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="F83" s="8" t="n">
-        <v>-0.7</v>
+        <v>0.6</v>
       </c>
       <c r="G83" s="8" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="H83" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I83" s="8" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="84">
@@ -3424,26 +3424,26 @@
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>Deandre Ayton</t>
+          <t>Donovan Clingan</t>
         </is>
       </c>
       <c r="D84" s="8" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E84" s="8" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="F84" s="8" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="G84" s="8" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="H84" s="6" t="b">
         <v>0</v>
       </c>
       <c r="I84" s="8" t="n">
-        <v>15.5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="85">
@@ -3459,17 +3459,17 @@
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>Sharpe / Clingan / Camara</t>
+          <t>Henderson / Holiday / Robert Williams III</t>
         </is>
       </c>
       <c r="D85" s="8" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E85" s="8" t="n">
-        <v>-2.1</v>
+        <v>-1.1</v>
       </c>
       <c r="F85" s="8" t="n">
-        <v>-0.4</v>
+        <v>-0.8</v>
       </c>
       <c r="G85" s="8" t="n">
         <v>0</v>
@@ -3498,22 +3498,22 @@
         </is>
       </c>
       <c r="D86" s="5" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E86" s="5" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="F86" s="5" t="n">
-        <v>-1.9</v>
+        <v>-0.9</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="H86" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I86" s="5" t="n">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="87">
@@ -3529,26 +3529,26 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>Collin Sexton</t>
+          <t>Darryn Peterson</t>
         </is>
       </c>
       <c r="D87" s="5" t="n">
         <v>30</v>
       </c>
       <c r="E87" s="5" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="F87" s="5" t="n">
-        <v>-1.5</v>
+        <v>-0.7</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H87" s="3" t="b">
         <v>0</v>
       </c>
       <c r="I87" s="5" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="88">
@@ -3571,10 +3571,10 @@
         <v>34</v>
       </c>
       <c r="E88" s="5" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="F88" s="5" t="n">
-        <v>0.2</v>
+        <v>-0.2</v>
       </c>
       <c r="G88" s="5" t="n">
         <v>0</v>
@@ -3583,7 +3583,7 @@
         <v>1</v>
       </c>
       <c r="I88" s="5" t="n">
-        <v>22.5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="89">
@@ -3599,17 +3599,17 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>Taylor Hendricks</t>
+          <t>Jaren Jackson Jr.</t>
         </is>
       </c>
       <c r="D89" s="5" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E89" s="5" t="n">
-        <v>-1.1</v>
+        <v>1.2</v>
       </c>
       <c r="F89" s="5" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="G89" s="5" t="n">
         <v>0</v>
@@ -3618,7 +3618,7 @@
         <v>0</v>
       </c>
       <c r="I89" s="5" t="n">
-        <v>11.5</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="90">
@@ -3634,26 +3634,26 @@
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>Walker Kessler</t>
+          <t>Jaxson Hayes</t>
         </is>
       </c>
       <c r="D90" s="5" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="F90" s="5" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="H90" s="3" t="b">
         <v>0</v>
       </c>
       <c r="I90" s="5" t="n">
-        <v>14.5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="91">
@@ -3669,17 +3669,17 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>Clarkson / Collins / Filipowski</t>
+          <t>Bailey / Nurkic / Bamba</t>
         </is>
       </c>
       <c r="D91" s="5" t="n">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E91" s="5" t="n">
         <v>-1.2</v>
       </c>
       <c r="F91" s="5" t="n">
-        <v>-1.8</v>
+        <v>-1</v>
       </c>
       <c r="G91" s="5" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
         </is>
       </c>
       <c r="D92" s="8" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E92" s="8" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="F92" s="8" t="n">
-        <v>-0.3</v>
+        <v>0.2</v>
       </c>
       <c r="G92" s="8" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="H92" s="6" t="b">
         <v>1</v>
       </c>
       <c r="I92" s="8" t="n">
-        <v>26.5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="93">
@@ -3743,19 +3743,19 @@
         </is>
       </c>
       <c r="D93" s="8" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E93" s="8" t="n">
         <v>0.6</v>
       </c>
       <c r="F93" s="8" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="G93" s="8" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H93" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I93" s="8" t="n">
         <v>15.5</v>
@@ -3774,26 +3774,26 @@
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>Andrew Wiggins</t>
+          <t>Yaxel Lendeborg</t>
         </is>
       </c>
       <c r="D94" s="8" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E94" s="8" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="F94" s="8" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="G94" s="8" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="H94" s="6" t="b">
         <v>0</v>
       </c>
       <c r="I94" s="8" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="95">
@@ -3809,26 +3809,26 @@
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>Jonathan Kuminga</t>
+          <t>Al Horford</t>
         </is>
       </c>
       <c r="D95" s="8" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E95" s="8" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="F95" s="8" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="G95" s="8" t="n">
-        <v>0</v>
+        <v>-0.7</v>
       </c>
       <c r="H95" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I95" s="8" t="n">
-        <v>16.5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="96">
@@ -3851,19 +3851,19 @@
         <v>30</v>
       </c>
       <c r="E96" s="8" t="n">
-        <v>0.4</v>
+        <v>-0.2</v>
       </c>
       <c r="F96" s="8" t="n">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="G96" s="8" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="H96" s="6" t="b">
         <v>0</v>
       </c>
       <c r="I96" s="8" t="n">
-        <v>15.5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="97">
@@ -3879,17 +3879,17 @@
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>Hield / Melton / Jackson-Davis</t>
+          <t>Melton / Brandon Williams / Gui Santos</t>
         </is>
       </c>
       <c r="D97" s="8" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="E97" s="8" t="n">
-        <v>0.3</v>
+        <v>-0.7</v>
       </c>
       <c r="F97" s="8" t="n">
-        <v>0.5</v>
+        <v>-0.5</v>
       </c>
       <c r="G97" s="8" t="n">
         <v>0</v>
@@ -3914,20 +3914,20 @@
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>James Harden</t>
+          <t>Darius Garland</t>
         </is>
       </c>
       <c r="D98" s="5" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E98" s="5" t="n">
-        <v>3.7</v>
+        <v>2</v>
       </c>
       <c r="F98" s="5" t="n">
-        <v>0.1</v>
+        <v>-0.9</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="H98" s="3" t="b">
         <v>1</v>
@@ -3949,26 +3949,26 @@
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>Norman Powell</t>
+          <t>Keaton Wagler</t>
         </is>
       </c>
       <c r="D99" s="5" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E99" s="5" t="n">
-        <v>2.2</v>
+        <v>0.2</v>
       </c>
       <c r="F99" s="5" t="n">
-        <v>-0.4</v>
+        <v>-0.8</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="H99" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I99" s="5" t="n">
-        <v>21.5</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="100">
@@ -3984,26 +3984,26 @@
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>Terance Mann</t>
+          <t>Derrick Jones Jr.</t>
         </is>
       </c>
       <c r="D100" s="5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E100" s="5" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="F100" s="5" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="H100" s="3" t="b">
         <v>0</v>
       </c>
       <c r="I100" s="5" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="101">
@@ -4019,26 +4019,26 @@
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>Derrick Jones Jr.</t>
+          <t>Rui Hachimura</t>
         </is>
       </c>
       <c r="D101" s="5" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E101" s="5" t="n">
-        <v>-0.3</v>
+        <v>1.6</v>
       </c>
       <c r="F101" s="5" t="n">
-        <v>1.4</v>
+        <v>-0.5</v>
       </c>
       <c r="G101" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H101" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I101" s="5" t="n">
-        <v>13.5</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="102">
@@ -4054,26 +4054,26 @@
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>Ivica Zubac</t>
+          <t>Brook Lopez</t>
         </is>
       </c>
       <c r="D102" s="5" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E102" s="5" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="F102" s="5" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="H102" s="3" t="b">
         <v>0</v>
       </c>
       <c r="I102" s="5" t="n">
-        <v>17.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="103">
@@ -4089,17 +4089,17 @@
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>Dunn / Coffey / Batum</t>
+          <t>Beal / Dunn / Broome</t>
         </is>
       </c>
       <c r="D103" s="5" t="n">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="E103" s="5" t="n">
         <v>-0.8</v>
       </c>
       <c r="F103" s="5" t="n">
-        <v>0.8</v>
+        <v>-0.6</v>
       </c>
       <c r="G103" s="5" t="n">
         <v>0</v>
@@ -4124,26 +4124,26 @@
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>D'Angelo Russell</t>
+          <t>Luka Doncic</t>
         </is>
       </c>
       <c r="D104" s="8" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E104" s="8" t="n">
-        <v>1.8</v>
+        <v>7.4</v>
       </c>
       <c r="F104" s="8" t="n">
-        <v>-1.1</v>
+        <v>0</v>
       </c>
       <c r="G104" s="8" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="H104" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I104" s="8" t="n">
-        <v>18.5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="105">
@@ -4163,22 +4163,22 @@
         </is>
       </c>
       <c r="D105" s="8" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E105" s="8" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="F105" s="8" t="n">
-        <v>-0.5</v>
+        <v>-0.4</v>
       </c>
       <c r="G105" s="8" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H105" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I105" s="8" t="n">
-        <v>19.5</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="106">
@@ -4194,26 +4194,26 @@
       </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
-          <t>Rui Hachimura</t>
+          <t>Quentin Grimes</t>
         </is>
       </c>
       <c r="D106" s="8" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E106" s="8" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="F106" s="8" t="n">
-        <v>-0.6</v>
+        <v>0.1</v>
       </c>
       <c r="G106" s="8" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="H106" s="6" t="b">
         <v>0</v>
       </c>
       <c r="I106" s="8" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="107">
@@ -4229,26 +4229,26 @@
       </c>
       <c r="C107" s="7" t="inlineStr">
         <is>
-          <t>LeBron James</t>
+          <t>Jake LaRavia</t>
         </is>
       </c>
       <c r="D107" s="8" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="E107" s="8" t="n">
-        <v>4.4</v>
+        <v>0.2</v>
       </c>
       <c r="F107" s="8" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="G107" s="8" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H107" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I107" s="8" t="n">
-        <v>24.5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="108">
@@ -4264,26 +4264,26 @@
       </c>
       <c r="C108" s="7" t="inlineStr">
         <is>
-          <t>Anthony Davis</t>
+          <t>Walker Kessler</t>
         </is>
       </c>
       <c r="D108" s="8" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="E108" s="8" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="F108" s="8" t="n">
-        <v>3.7</v>
+        <v>1.9</v>
       </c>
       <c r="G108" s="8" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="H108" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I108" s="8" t="n">
-        <v>24.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="109">
@@ -4299,17 +4299,17 @@
       </c>
       <c r="C109" s="7" t="inlineStr">
         <is>
-          <t>Vincent / Knecht / Hayes</t>
+          <t>Thybulle / Mamukelashvili / Looney</t>
         </is>
       </c>
       <c r="D109" s="8" t="n">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="E109" s="8" t="n">
-        <v>-1.6</v>
+        <v>-0.9</v>
       </c>
       <c r="F109" s="8" t="n">
-        <v>-0.4</v>
+        <v>-0.8</v>
       </c>
       <c r="G109" s="8" t="n">
         <v>0</v>
@@ -4334,26 +4334,26 @@
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>Tyus Jones</t>
+          <t>Devin Booker</t>
         </is>
       </c>
       <c r="D110" s="5" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E110" s="5" t="n">
-        <v>1.7</v>
+        <v>4.4</v>
       </c>
       <c r="F110" s="5" t="n">
-        <v>-0.8</v>
+        <v>-0.6</v>
       </c>
       <c r="G110" s="5" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="H110" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I110" s="5" t="n">
-        <v>17.5</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="111">
@@ -4369,26 +4369,26 @@
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>Devin Booker</t>
+          <t>Jalen Green</t>
         </is>
       </c>
       <c r="D111" s="5" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E111" s="5" t="n">
-        <v>4.3</v>
+        <v>1.5</v>
       </c>
       <c r="F111" s="5" t="n">
-        <v>-0.2</v>
+        <v>-1.2</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="H111" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I111" s="5" t="n">
-        <v>26.5</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="112">
@@ -4404,26 +4404,26 @@
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>Bradley Beal</t>
+          <t>Dillon Brooks</t>
         </is>
       </c>
       <c r="D112" s="5" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E112" s="5" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="F112" s="5" t="n">
-        <v>-0.4</v>
+        <v>1.2</v>
       </c>
       <c r="G112" s="5" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H112" s="3" t="b">
         <v>0</v>
       </c>
       <c r="I112" s="5" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="113">
@@ -4439,26 +4439,26 @@
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>Kevin Durant</t>
+          <t>Miles Bridges</t>
         </is>
       </c>
       <c r="D113" s="5" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E113" s="5" t="n">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="F113" s="5" t="n">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="H113" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I113" s="5" t="n">
-        <v>26.5</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="114">
@@ -4474,17 +4474,17 @@
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>Jusuf Nurkic</t>
+          <t>Khaman Maluach</t>
         </is>
       </c>
       <c r="D114" s="5" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E114" s="5" t="n">
-        <v>0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="F114" s="5" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G114" s="5" t="n">
         <v>0</v>
@@ -4493,7 +4493,7 @@
         <v>0</v>
       </c>
       <c r="I114" s="5" t="n">
-        <v>14.5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="115">
@@ -4509,17 +4509,17 @@
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>Allen / O'Neale / Plumlee</t>
+          <t>Gillespie / Ighodaro / Kennard</t>
         </is>
       </c>
       <c r="D115" s="5" t="n">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="E115" s="5" t="n">
-        <v>-0.5</v>
+        <v>-1.1</v>
       </c>
       <c r="F115" s="5" t="n">
-        <v>0.2</v>
+        <v>-0.8</v>
       </c>
       <c r="G115" s="5" t="n">
         <v>0</v>
@@ -4544,26 +4544,26 @@
       </c>
       <c r="C116" s="7" t="inlineStr">
         <is>
-          <t>De'Aaron Fox</t>
+          <t>Darius Acuff Jr.</t>
         </is>
       </c>
       <c r="D116" s="8" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E116" s="8" t="n">
-        <v>3.8</v>
+        <v>0.2</v>
       </c>
       <c r="F116" s="8" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="G116" s="8" t="n">
         <v>0.8</v>
       </c>
-      <c r="G116" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="H116" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I116" s="8" t="n">
-        <v>25.5</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="117">
@@ -4579,26 +4579,26 @@
       </c>
       <c r="C117" s="7" t="inlineStr">
         <is>
-          <t>Kevin Huerter</t>
+          <t>Zach LaVine</t>
         </is>
       </c>
       <c r="D117" s="8" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E117" s="8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F117" s="8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G117" s="8" t="n">
         <v>0.6</v>
       </c>
-      <c r="F117" s="8" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="G117" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="H117" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I117" s="8" t="n">
-        <v>14.5</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="118">
@@ -4614,26 +4614,26 @@
       </c>
       <c r="C118" s="7" t="inlineStr">
         <is>
-          <t>DeMar DeRozan</t>
+          <t>De'Andre Hunter</t>
         </is>
       </c>
       <c r="D118" s="8" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E118" s="8" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="F118" s="8" t="n">
-        <v>-0.3</v>
+        <v>0.2</v>
       </c>
       <c r="G118" s="8" t="n">
         <v>0</v>
       </c>
       <c r="H118" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I118" s="8" t="n">
-        <v>21.5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="119">
@@ -4653,22 +4653,22 @@
         </is>
       </c>
       <c r="D119" s="8" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E119" s="8" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="F119" s="8" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="G119" s="8" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="H119" s="6" t="b">
         <v>0</v>
       </c>
       <c r="I119" s="8" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="120">
@@ -4688,22 +4688,22 @@
         </is>
       </c>
       <c r="D120" s="8" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E120" s="8" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="F120" s="8" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="G120" s="8" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="H120" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I120" s="8" t="n">
-        <v>22.5</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="121">
@@ -4719,17 +4719,17 @@
       </c>
       <c r="C121" s="7" t="inlineStr">
         <is>
-          <t>Monk / Ellis / Lyles</t>
+          <t>Monk / Clifford / Raynaud</t>
         </is>
       </c>
       <c r="D121" s="8" t="n">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="E121" s="8" t="n">
-        <v>-0.6</v>
+        <v>-1.2</v>
       </c>
       <c r="F121" s="8" t="n">
-        <v>-0.2</v>
+        <v>-1</v>
       </c>
       <c r="G121" s="8" t="n">
         <v>0</v>
@@ -4754,26 +4754,26 @@
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>Trae Young</t>
+          <t>CJ McCollum</t>
         </is>
       </c>
       <c r="D122" s="5" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E122" s="5" t="n">
-        <v>4.6</v>
+        <v>1.4</v>
       </c>
       <c r="F122" s="5" t="n">
-        <v>-2.2</v>
+        <v>-0.6</v>
       </c>
       <c r="G122" s="5" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H122" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I122" s="5" t="n">
-        <v>25.5</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="123">
@@ -4789,26 +4789,26 @@
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>Dyson Daniels</t>
+          <t>Nickeil Alexander-Walker</t>
         </is>
       </c>
       <c r="D123" s="5" t="n">
         <v>30</v>
       </c>
       <c r="E123" s="5" t="n">
-        <v>-0.5</v>
+        <v>1.2</v>
       </c>
       <c r="F123" s="5" t="n">
-        <v>2.4</v>
+        <v>0.2</v>
       </c>
       <c r="G123" s="5" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="H123" s="3" t="b">
         <v>0</v>
       </c>
       <c r="I123" s="5" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="124">
@@ -4824,26 +4824,26 @@
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>Zaccharie Risacher</t>
+          <t>Dyson Daniels</t>
         </is>
       </c>
       <c r="D124" s="5" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E124" s="5" t="n">
-        <v>-0.4</v>
+        <v>0.2</v>
       </c>
       <c r="F124" s="5" t="n">
-        <v>0.2</v>
+        <v>1.9</v>
       </c>
       <c r="G124" s="5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H124" s="3" t="b">
         <v>0</v>
       </c>
       <c r="I124" s="5" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="125">
@@ -4863,22 +4863,22 @@
         </is>
       </c>
       <c r="D125" s="5" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E125" s="5" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="F125" s="5" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="G125" s="5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H125" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I125" s="5" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="126">
@@ -4894,26 +4894,26 @@
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>Clint Capela</t>
+          <t>Onyeka Okongwu</t>
         </is>
       </c>
       <c r="D126" s="5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E126" s="5" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="F126" s="5" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="G126" s="5" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="H126" s="3" t="b">
         <v>0</v>
       </c>
       <c r="I126" s="5" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="127">
@@ -4929,17 +4929,17 @@
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>Bogdanovic / Hunter / Okongwu</t>
+          <t>Dort / Finney-Smith / Wiggins</t>
         </is>
       </c>
       <c r="D127" s="5" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E127" s="5" t="n">
-        <v>0.2</v>
+        <v>-0.7</v>
       </c>
       <c r="F127" s="5" t="n">
-        <v>-1.3</v>
+        <v>-0.5</v>
       </c>
       <c r="G127" s="5" t="n">
         <v>0</v>
@@ -4964,26 +4964,26 @@
       </c>
       <c r="C128" s="7" t="inlineStr">
         <is>
-          <t>LaMelo Ball</t>
+          <t>Coby White</t>
         </is>
       </c>
       <c r="D128" s="8" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E128" s="8" t="n">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="F128" s="8" t="n">
-        <v>-1.4</v>
+        <v>-1</v>
       </c>
       <c r="G128" s="8" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="H128" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I128" s="8" t="n">
-        <v>25.5</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="129">
@@ -4999,26 +4999,26 @@
       </c>
       <c r="C129" s="7" t="inlineStr">
         <is>
-          <t>Josh Green</t>
+          <t>Kon Knueppel</t>
         </is>
       </c>
       <c r="D129" s="8" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E129" s="8" t="n">
-        <v>-0.6</v>
+        <v>1.7</v>
       </c>
       <c r="F129" s="8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G129" s="8" t="n">
         <v>0.3</v>
       </c>
-      <c r="G129" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="H129" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I129" s="8" t="n">
-        <v>13.5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="130">
@@ -5041,19 +5041,19 @@
         <v>34</v>
       </c>
       <c r="E130" s="8" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="F130" s="8" t="n">
-        <v>-0.8</v>
+        <v>-0.3</v>
       </c>
       <c r="G130" s="8" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="H130" s="6" t="b">
         <v>1</v>
       </c>
       <c r="I130" s="8" t="n">
-        <v>20.5</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="131">
@@ -5069,17 +5069,17 @@
       </c>
       <c r="C131" s="7" t="inlineStr">
         <is>
-          <t>Miles Bridges</t>
+          <t>Naz Reid</t>
         </is>
       </c>
       <c r="D131" s="8" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E131" s="8" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F131" s="8" t="n">
-        <v>-0.9</v>
+        <v>0.2</v>
       </c>
       <c r="G131" s="8" t="n">
         <v>0</v>
@@ -5088,7 +5088,7 @@
         <v>0</v>
       </c>
       <c r="I131" s="8" t="n">
-        <v>18.5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="132">
@@ -5104,26 +5104,26 @@
       </c>
       <c r="C132" s="7" t="inlineStr">
         <is>
-          <t>Mark Williams</t>
+          <t>Moussa Diabate</t>
         </is>
       </c>
       <c r="D132" s="8" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E132" s="8" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="F132" s="8" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="G132" s="8" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="H132" s="6" t="b">
         <v>0</v>
       </c>
       <c r="I132" s="8" t="n">
-        <v>15.5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="133">
@@ -5139,17 +5139,17 @@
       </c>
       <c r="C133" s="7" t="inlineStr">
         <is>
-          <t>Mann / Micic / Richards</t>
+          <t>Schroder / Allen / James</t>
         </is>
       </c>
       <c r="D133" s="8" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="E133" s="8" t="n">
-        <v>-2.2</v>
+        <v>-0.8</v>
       </c>
       <c r="F133" s="8" t="n">
-        <v>-1.2</v>
+        <v>-0.6</v>
       </c>
       <c r="G133" s="8" t="n">
         <v>0</v>
@@ -5174,26 +5174,26 @@
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>Terry Rozier</t>
+          <t>Davion Mitchell</t>
         </is>
       </c>
       <c r="D134" s="5" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E134" s="5" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="F134" s="5" t="n">
-        <v>-0.4</v>
+        <v>0.4</v>
       </c>
       <c r="G134" s="5" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="H134" s="3" t="b">
         <v>0</v>
       </c>
       <c r="I134" s="5" t="n">
-        <v>16.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="135">
@@ -5209,26 +5209,26 @@
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>Tyler Herro</t>
+          <t>Klay Thompson</t>
         </is>
       </c>
       <c r="D135" s="5" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E135" s="5" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="F135" s="5" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="G135" s="5" t="n">
         <v>-0.3</v>
       </c>
-      <c r="G135" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="H135" s="3" t="b">
         <v>0</v>
       </c>
       <c r="I135" s="5" t="n">
-        <v>20.5</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="136">
@@ -5244,26 +5244,26 @@
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>Jimmy Butler</t>
+          <t>Andrew Wiggins</t>
         </is>
       </c>
       <c r="D136" s="5" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E136" s="5" t="n">
-        <v>3.6</v>
+        <v>0.6</v>
       </c>
       <c r="F136" s="5" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="G136" s="5" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="H136" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I136" s="5" t="n">
-        <v>20.5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="137">
@@ -5279,26 +5279,26 @@
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>Nikola Jovic</t>
+          <t>Giannis Antetokounmpo</t>
         </is>
       </c>
       <c r="D137" s="5" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E137" s="5" t="n">
-        <v>0.2</v>
+        <v>6.4</v>
       </c>
       <c r="F137" s="5" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="G137" s="5" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="H137" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I137" s="5" t="n">
-        <v>13.5</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="138">
@@ -5318,22 +5318,22 @@
         </is>
       </c>
       <c r="D138" s="5" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E138" s="5" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="F138" s="5" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="G138" s="5" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H138" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I138" s="5" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="139">
@@ -5349,17 +5349,17 @@
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>Jaquez Jr. / Robinson / Highsmith</t>
+          <t>Hardaway Jr. / Larsson / Dru Smith</t>
         </is>
       </c>
       <c r="D139" s="5" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="E139" s="5" t="n">
-        <v>-1.1</v>
+        <v>-0.9</v>
       </c>
       <c r="F139" s="5" t="n">
-        <v>0.9</v>
+        <v>-0.8</v>
       </c>
       <c r="G139" s="5" t="n">
         <v>0</v>
@@ -5388,22 +5388,22 @@
         </is>
       </c>
       <c r="D140" s="8" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E140" s="8" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="F140" s="8" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="G140" s="8" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="H140" s="6" t="b">
         <v>0</v>
       </c>
       <c r="I140" s="8" t="n">
-        <v>16.5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="141">
@@ -5419,26 +5419,26 @@
       </c>
       <c r="C141" s="7" t="inlineStr">
         <is>
-          <t>Kentavious Caldwell-Pope</t>
+          <t>Desmond Bane</t>
         </is>
       </c>
       <c r="D141" s="8" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E141" s="8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F141" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="F141" s="8" t="n">
-        <v>1.8</v>
-      </c>
       <c r="G141" s="8" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H141" s="6" t="b">
         <v>0</v>
       </c>
       <c r="I141" s="8" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="142">
@@ -5461,13 +5461,13 @@
         <v>34</v>
       </c>
       <c r="E142" s="8" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="F142" s="8" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="G142" s="8" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H142" s="6" t="b">
         <v>1</v>
@@ -5496,19 +5496,19 @@
         <v>35</v>
       </c>
       <c r="E143" s="8" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="F143" s="8" t="n">
-        <v>0.8</v>
+        <v>-0.1</v>
       </c>
       <c r="G143" s="8" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="H143" s="6" t="b">
         <v>1</v>
       </c>
       <c r="I143" s="8" t="n">
-        <v>24.5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="144">
@@ -5528,22 +5528,22 @@
         </is>
       </c>
       <c r="D144" s="8" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E144" s="8" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="F144" s="8" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="G144" s="8" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="H144" s="6" t="b">
         <v>0</v>
       </c>
       <c r="I144" s="8" t="n">
-        <v>15.5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="145">
@@ -5559,17 +5559,17 @@
       </c>
       <c r="C145" s="7" t="inlineStr">
         <is>
-          <t>Isaac / Anthony / Bitadze</t>
+          <t>Black / da Silva / Vucevic</t>
         </is>
       </c>
       <c r="D145" s="8" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E145" s="8" t="n">
-        <v>-1.6</v>
+        <v>-1.1</v>
       </c>
       <c r="F145" s="8" t="n">
-        <v>1.4</v>
+        <v>-0.8</v>
       </c>
       <c r="G145" s="8" t="n">
         <v>0</v>
@@ -5594,26 +5594,26 @@
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>Jordan Poole</t>
+          <t>Trae Young</t>
         </is>
       </c>
       <c r="D146" s="5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E146" s="5" t="n">
-        <v>0.4</v>
+        <v>4</v>
       </c>
       <c r="F146" s="5" t="n">
-        <v>-2.3</v>
+        <v>-1.5</v>
       </c>
       <c r="G146" s="5" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="H146" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I146" s="5" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="147">
@@ -5629,20 +5629,20 @@
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>Malcolm Brogdon</t>
+          <t>Kyshawn George</t>
         </is>
       </c>
       <c r="D147" s="5" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E147" s="5" t="n">
         <v>0.6</v>
       </c>
       <c r="F147" s="5" t="n">
-        <v>-0.9</v>
+        <v>0.9</v>
       </c>
       <c r="G147" s="5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H147" s="3" t="b">
         <v>0</v>
@@ -5664,26 +5664,26 @@
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>Bilal Coulibaly</t>
+          <t>AJ Dybantsa</t>
         </is>
       </c>
       <c r="D148" s="5" t="n">
         <v>30</v>
       </c>
       <c r="E148" s="5" t="n">
-        <v>-1.2</v>
+        <v>1</v>
       </c>
       <c r="F148" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G148" s="5" t="n">
         <v>0.7</v>
       </c>
-      <c r="G148" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="H148" s="3" t="b">
         <v>0</v>
       </c>
       <c r="I148" s="5" t="n">
-        <v>13.5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="149">
@@ -5699,26 +5699,26 @@
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>Kyle Kuzma</t>
+          <t>Anthony Davis</t>
         </is>
       </c>
       <c r="D149" s="5" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E149" s="5" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="F149" s="5" t="n">
-        <v>-1.4</v>
+        <v>2</v>
       </c>
       <c r="G149" s="5" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="H149" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I149" s="5" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="150">
@@ -5738,22 +5738,22 @@
         </is>
       </c>
       <c r="D150" s="5" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E150" s="5" t="n">
-        <v>-1.6</v>
+        <v>0.2</v>
       </c>
       <c r="F150" s="5" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="G150" s="5" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H150" s="3" t="b">
         <v>0</v>
       </c>
       <c r="I150" s="5" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="151">
@@ -5769,17 +5769,17 @@
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>Valanciunas / Kispert / Carrington</t>
+          <t>Coulibaly / Ayton / Middleton</t>
         </is>
       </c>
       <c r="D151" s="5" t="n">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E151" s="5" t="n">
-        <v>-1.8</v>
+        <v>-1.2</v>
       </c>
       <c r="F151" s="5" t="n">
-        <v>-1.5</v>
+        <v>-1</v>
       </c>
       <c r="G151" s="5" t="n">
         <v>0</v>
@@ -5804,26 +5804,26 @@
       </c>
       <c r="C152" s="7" t="inlineStr">
         <is>
-          <t>Luka Doncic</t>
+          <t>Kyrie Irving</t>
         </is>
       </c>
       <c r="D152" s="8" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="E152" s="8" t="n">
-        <v>6.4</v>
+        <v>3.8</v>
       </c>
       <c r="F152" s="8" t="n">
-        <v>0.4</v>
+        <v>-0.7</v>
       </c>
       <c r="G152" s="8" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H152" s="6" t="b">
         <v>1</v>
       </c>
       <c r="I152" s="8" t="n">
-        <v>31.5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="153">
@@ -5839,26 +5839,26 @@
       </c>
       <c r="C153" s="7" t="inlineStr">
         <is>
-          <t>Kyrie Irving</t>
+          <t>Max Christie</t>
         </is>
       </c>
       <c r="D153" s="8" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E153" s="8" t="n">
-        <v>4.1</v>
+        <v>0.7</v>
       </c>
       <c r="F153" s="8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G153" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="G153" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="H153" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I153" s="8" t="n">
-        <v>24.5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="154">
@@ -5874,26 +5874,26 @@
       </c>
       <c r="C154" s="7" t="inlineStr">
         <is>
-          <t>Klay Thompson</t>
+          <t>Cooper Flagg</t>
         </is>
       </c>
       <c r="D154" s="8" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E154" s="8" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="F154" s="8" t="n">
-        <v>-0.5</v>
+        <v>1.3</v>
       </c>
       <c r="G154" s="8" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H154" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I154" s="8" t="n">
-        <v>16.5</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="155">
@@ -5913,22 +5913,22 @@
         </is>
       </c>
       <c r="D155" s="8" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E155" s="8" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="F155" s="8" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="G155" s="8" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H155" s="6" t="b">
         <v>0</v>
       </c>
       <c r="I155" s="8" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="156">
@@ -5951,19 +5951,19 @@
         <v>26</v>
       </c>
       <c r="E156" s="8" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="F156" s="8" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="G156" s="8" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="H156" s="6" t="b">
         <v>0</v>
       </c>
       <c r="I156" s="8" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="157">
@@ -5979,17 +5979,17 @@
       </c>
       <c r="C157" s="7" t="inlineStr">
         <is>
-          <t>Lively II / Grimes / Marshall</t>
+          <t>Marshall / Risacher / Aldama</t>
         </is>
       </c>
       <c r="D157" s="8" t="n">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="E157" s="8" t="n">
-        <v>-0.6</v>
+        <v>-0.7</v>
       </c>
       <c r="F157" s="8" t="n">
-        <v>0.7</v>
+        <v>-0.5</v>
       </c>
       <c r="G157" s="8" t="n">
         <v>0</v>
@@ -6018,22 +6018,22 @@
         </is>
       </c>
       <c r="D158" s="5" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E158" s="5" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="F158" s="5" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="G158" s="5" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H158" s="3" t="b">
         <v>0</v>
       </c>
       <c r="I158" s="5" t="n">
-        <v>20.5</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="159">
@@ -6049,7 +6049,7 @@
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>Jalen Green</t>
+          <t>Amen Thompson</t>
         </is>
       </c>
       <c r="D159" s="5" t="n">
@@ -6059,16 +6059,16 @@
         <v>1.5</v>
       </c>
       <c r="F159" s="5" t="n">
-        <v>-0.2</v>
+        <v>2</v>
       </c>
       <c r="G159" s="5" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="H159" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I159" s="5" t="n">
-        <v>21.5</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="160">
@@ -6084,26 +6084,26 @@
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>Dillon Brooks</t>
+          <t>Kevin Durant</t>
         </is>
       </c>
       <c r="D160" s="5" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E160" s="5" t="n">
-        <v>-0.6</v>
+        <v>4.8</v>
       </c>
       <c r="F160" s="5" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="G160" s="5" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="H160" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I160" s="5" t="n">
-        <v>14.5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="161">
@@ -6123,22 +6123,22 @@
         </is>
       </c>
       <c r="D161" s="5" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E161" s="5" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="F161" s="5" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="G161" s="5" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H161" s="3" t="b">
         <v>0</v>
       </c>
       <c r="I161" s="5" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="162">
@@ -6158,22 +6158,22 @@
         </is>
       </c>
       <c r="D162" s="5" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E162" s="5" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="F162" s="5" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="G162" s="5" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="H162" s="3" t="b">
         <v>1</v>
       </c>
       <c r="I162" s="5" t="n">
-        <v>20.5</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="163">
@@ -6189,17 +6189,17 @@
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>Thompson / Eason / Sheppard</t>
+          <t>Smart / Sheppard / Adams</t>
         </is>
       </c>
       <c r="D163" s="5" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E163" s="5" t="n">
         <v>-0.8</v>
       </c>
       <c r="F163" s="5" t="n">
-        <v>1.5</v>
+        <v>-0.6</v>
       </c>
       <c r="G163" s="5" t="n">
         <v>0</v>
@@ -6224,26 +6224,26 @@
       </c>
       <c r="C164" s="7" t="inlineStr">
         <is>
-          <t>Ja Morant</t>
+          <t>Ty Jerome</t>
         </is>
       </c>
       <c r="D164" s="8" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E164" s="8" t="n">
-        <v>3.9</v>
+        <v>1.2</v>
       </c>
       <c r="F164" s="8" t="n">
-        <v>-0.3</v>
+        <v>-0.4</v>
       </c>
       <c r="G164" s="8" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H164" s="6" t="b">
         <v>1</v>
       </c>
       <c r="I164" s="8" t="n">
-        <v>24.5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="165">
@@ -6259,26 +6259,26 @@
       </c>
       <c r="C165" s="7" t="inlineStr">
         <is>
-          <t>Desmond Bane</t>
+          <t>Jaylen Wells</t>
         </is>
       </c>
       <c r="D165" s="8" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E165" s="8" t="n">
-        <v>2.8</v>
+        <v>0.4</v>
       </c>
       <c r="F165" s="8" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="G165" s="8" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="H165" s="6" t="b">
         <v>0</v>
       </c>
       <c r="I165" s="8" t="n">
-        <v>21.5</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="166">
@@ -6294,26 +6294,26 @@
       </c>
       <c r="C166" s="7" t="inlineStr">
         <is>
-          <t>Marcus Smart</t>
+          <t>Cedric Coward</t>
         </is>
       </c>
       <c r="D166" s="8" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E166" s="8" t="n">
-        <v>-0.4</v>
+        <v>0.5</v>
       </c>
       <c r="F166" s="8" t="n">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="G166" s="8" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H166" s="6" t="b">
         <v>0</v>
       </c>
       <c r="I166" s="8" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="167">
@@ -6329,26 +6329,26 @@
       </c>
       <c r="C167" s="7" t="inlineStr">
         <is>
-          <t>Jaren Jackson Jr.</t>
+          <t>Cameron Boozer</t>
         </is>
       </c>
       <c r="D167" s="8" t="n">
         <v>32</v>
       </c>
       <c r="E167" s="8" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="F167" s="8" t="n">
-        <v>2.8</v>
+        <v>0.3</v>
       </c>
       <c r="G167" s="8" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H167" s="6" t="b">
         <v>1</v>
       </c>
       <c r="I167" s="8" t="n">
-        <v>21.5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="168">
@@ -6371,13 +6371,13 @@
         <v>26</v>
       </c>
       <c r="E168" s="8" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="F168" s="8" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="G168" s="8" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="H168" s="6" t="b">
         <v>0</v>
@@ -6399,17 +6399,17 @@
       </c>
       <c r="C169" s="7" t="inlineStr">
         <is>
-          <t>Aldama / Pippen Jr. / Clarke</t>
+          <t>Grant / Russell / Stewart</t>
         </is>
       </c>
       <c r="D169" s="8" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="E169" s="8" t="n">
-        <v>-0.6</v>
+        <v>-0.9</v>
       </c>
       <c r="F169" s="8" t="n">
-        <v>0.3</v>
+        <v>-0.8</v>
       </c>
       <c r="G169" s="8" t="n">
         <v>0</v>
@@ -6438,22 +6438,22 @@
         </is>
       </c>
       <c r="D170" s="5" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E170" s="5" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="F170" s="5" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="G170" s="5" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="H170" s="3" t="b">
         <v>0</v>
       </c>
       <c r="I170" s="5" t="n">
-        <v>19.5</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="171">
@@ -6469,26 +6469,26 @@
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>CJ McCollum</t>
+          <t>Trey Murphy III</t>
         </is>
       </c>
       <c r="D171" s="5" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E171" s="5" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="F171" s="5" t="n">
-        <v>-0.6</v>
+        <v>0.5</v>
       </c>
       <c r="G171" s="5" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H171" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I171" s="5" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="172">
@@ -6504,26 +6504,26 @@
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>Brandon Ingram</t>
+          <t>Herbert Jones</t>
         </is>
       </c>
       <c r="D172" s="5" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E172" s="5" t="n">
-        <v>2.2</v>
+        <v>0.2</v>
       </c>
       <c r="F172" s="5" t="n">
-        <v>-0.2</v>
+        <v>1.9</v>
       </c>
       <c r="G172" s="5" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H172" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I172" s="5" t="n">
-        <v>21.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="173">
@@ -6539,26 +6539,26 @@
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>Herbert Jones</t>
+          <t>Zion Williamson</t>
         </is>
       </c>
       <c r="D173" s="5" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E173" s="5" t="n">
-        <v>0.2</v>
+        <v>3.4</v>
       </c>
       <c r="F173" s="5" t="n">
-        <v>2.9</v>
+        <v>-0.5</v>
       </c>
       <c r="G173" s="5" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="H173" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I173" s="5" t="n">
-        <v>15.5</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="174">
@@ -6574,26 +6574,26 @@
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>Zion Williamson</t>
+          <t>Yves Missi</t>
         </is>
       </c>
       <c r="D174" s="5" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="E174" s="5" t="n">
-        <v>3.4</v>
+        <v>0.1</v>
       </c>
       <c r="F174" s="5" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="G174" s="5" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="H174" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I174" s="5" t="n">
-        <v>22.5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="175">
@@ -6609,17 +6609,17 @@
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>Murphy III / Alvarado / Missi</t>
+          <t>Fears / Queen / Mathurin</t>
         </is>
       </c>
       <c r="D175" s="5" t="n">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="E175" s="5" t="n">
-        <v>-0.9</v>
+        <v>-1.1</v>
       </c>
       <c r="F175" s="5" t="n">
-        <v>0.2</v>
+        <v>-0.8</v>
       </c>
       <c r="G175" s="5" t="n">
         <v>0</v>
@@ -6644,26 +6644,26 @@
       </c>
       <c r="C176" s="7" t="inlineStr">
         <is>
-          <t>Chris Paul</t>
+          <t>De'Aaron Fox</t>
         </is>
       </c>
       <c r="D176" s="8" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E176" s="8" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="F176" s="8" t="n">
-        <v>0.4</v>
+        <v>-0.1</v>
       </c>
       <c r="G176" s="8" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="H176" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I176" s="8" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="177">
@@ -6679,26 +6679,26 @@
       </c>
       <c r="C177" s="7" t="inlineStr">
         <is>
-          <t>Devin Vassell</t>
+          <t>Stephon Castle</t>
         </is>
       </c>
       <c r="D177" s="8" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E177" s="8" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="F177" s="8" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="G177" s="8" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="H177" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I177" s="8" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="178">
@@ -6714,26 +6714,26 @@
       </c>
       <c r="C178" s="7" t="inlineStr">
         <is>
-          <t>Harrison Barnes</t>
+          <t>Dylan Harper</t>
         </is>
       </c>
       <c r="D178" s="8" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E178" s="8" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F178" s="8" t="n">
-        <v>-0.4</v>
+        <v>0.2</v>
       </c>
       <c r="G178" s="8" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="H178" s="6" t="b">
         <v>0</v>
       </c>
       <c r="I178" s="8" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="179">
@@ -6749,26 +6749,26 @@
       </c>
       <c r="C179" s="7" t="inlineStr">
         <is>
-          <t>Jeremy Sochan</t>
+          <t>Devin Vassell</t>
         </is>
       </c>
       <c r="D179" s="8" t="n">
         <v>30</v>
       </c>
       <c r="E179" s="8" t="n">
-        <v>-0.8</v>
+        <v>1</v>
       </c>
       <c r="F179" s="8" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="G179" s="8" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H179" s="6" t="b">
         <v>0</v>
       </c>
       <c r="I179" s="8" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="180">
@@ -6791,19 +6791,19 @@
         <v>34</v>
       </c>
       <c r="E180" s="8" t="n">
-        <v>2.9</v>
+        <v>4.6</v>
       </c>
       <c r="F180" s="8" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="G180" s="8" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="H180" s="6" t="b">
         <v>1</v>
       </c>
       <c r="I180" s="8" t="n">
-        <v>23.5</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="181">
@@ -6819,17 +6819,17 @@
       </c>
       <c r="C181" s="7" t="inlineStr">
         <is>
-          <t>Johnson / Castle / Tre Jones</t>
+          <t>Champagnie / Keldon Johnson / Harris</t>
         </is>
       </c>
       <c r="D181" s="8" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E181" s="8" t="n">
-        <v>-1.4</v>
+        <v>-1.2</v>
       </c>
       <c r="F181" s="8" t="n">
-        <v>-0.1</v>
+        <v>-1</v>
       </c>
       <c r="G181" s="8" t="n">
         <v>0</v>
